--- a/story_simulator/data/phonemes_table.xlsx
+++ b/story_simulator/data/phonemes_table.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhafen/repos/story-simulator/story_simulator/generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhafen/repos/story-simulator/story_simulator/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="1680" windowWidth="24560" windowHeight="12880" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="14100" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1605,7 +1605,7 @@
         <v>143</v>
       </c>
       <c r="D42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>97</v>
